--- a/workbooks/professor_collection_queue.xlsx
+++ b/workbooks/professor_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:46:20Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:46:20Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:53:15Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:53:15Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/professor_collection_queue.xlsx
+++ b/workbooks/professor_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:53:15Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:53:15Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -158,27 +158,27 @@
       </c>
       <c r="E2" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://cs.fudan.edu.cn</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="0">
         <is>
-          <t>Elite comprehensive research university and strong for supervisor-led applications</t>
+          <t>Official CS profiles partially extracted; continue by department</t>
         </is>
       </c>
     </row>
@@ -205,27 +205,27 @@
       </c>
       <c r="E3" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G3" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://cs.hit.edu.cn</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="0">
         <is>
-          <t>Strong engineering and science option with high research output</t>
+          <t>Official CS faculty directory identified; continue detailed profile extraction</t>
         </is>
       </c>
     </row>
@@ -252,27 +252,27 @@
       </c>
       <c r="E4" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G4" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://cs.nju.edu.cn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="0">
         <is>
-          <t>Top research university with strong science and humanities reputation</t>
+          <t>Official CS profiles partially extracted; continue by department</t>
         </is>
       </c>
     </row>
@@ -299,27 +299,27 @@
       </c>
       <c r="E5" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G5" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://eecs.pku.edu.cn</t>
         </is>
       </c>
       <c r="H5" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr" s="0">
         <is>
-          <t>Top-tier option with intense competition and strong academic prestige</t>
+          <t>Official PKU EECS computer science first pass extracted; other departments still pending</t>
         </is>
       </c>
     </row>
@@ -346,27 +346,27 @@
       </c>
       <c r="E6" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://cs.sjtu.edu.cn</t>
         </is>
       </c>
       <c r="H6" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="0">
         <is>
-          <t>Excellent for engineering interdisciplinary research and international visibility</t>
+          <t>Official CS profiles partially extracted; continue by research group</t>
         </is>
       </c>
     </row>
@@ -393,27 +393,27 @@
       </c>
       <c r="E7" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G7" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://www.cs.tsinghua.edu.cn</t>
         </is>
       </c>
       <c r="H7" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr" s="0">
         <is>
-          <t>Top engineering and technology target with very high competition</t>
+          <t>Official CS and media faculty profiles partially extracted</t>
         </is>
       </c>
     </row>
@@ -440,27 +440,27 @@
       </c>
       <c r="E8" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://cs.ustc.edu.cn</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="0">
         <is>
-          <t>Excellent for science-focused applications and lab quality</t>
+          <t>Official CS faculty profiles partially extracted; continue by professor page</t>
         </is>
       </c>
     </row>
@@ -487,27 +487,27 @@
       </c>
       <c r="E9" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G9" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://cs.xjtu.edu.cn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr" s="0">
         <is>
-          <t>Strong research university with comparatively broader access than top Beijing and Shanghai options</t>
+          <t>Official CS and AI school profiles partially extracted; continue by department</t>
         </is>
       </c>
     </row>
@@ -534,27 +534,27 @@
       </c>
       <c r="E10" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G10" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://www.cs.zju.edu.cn</t>
         </is>
       </c>
       <c r="H10" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="0">
         <is>
-          <t>Excellent broad-spectrum research university with strong STEM profile</t>
+          <t>Official computer science faculty profiles partially extracted; continue by institute</t>
         </is>
       </c>
     </row>

--- a/workbooks/professor_collection_queue.xlsx
+++ b/workbooks/professor_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:08:22Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:08:22Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/professor_collection_queue.xlsx
+++ b/workbooks/professor_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:08:22Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:08:22Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -210,7 +210,7 @@
       </c>
       <c r="F3" t="inlineStr" s="0">
         <is>
-          <t>Computer science related faculty first pass</t>
+          <t>Computer science and energy related faculty first pass</t>
         </is>
       </c>
       <c r="G3" t="inlineStr" s="0">
@@ -225,7 +225,7 @@
       </c>
       <c r="I3" t="inlineStr" s="0">
         <is>
-          <t>Official CS faculty directory identified; continue detailed profile extraction</t>
+          <t>Official CS faculty directory identified and local HIT Shenzhen energy rows imported; continue detailed profile extraction</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="F9" t="inlineStr" s="0">
         <is>
-          <t>Computer science related faculty first pass</t>
+          <t>Computer science and thermophysics faculty first pass</t>
         </is>
       </c>
       <c r="G9" t="inlineStr" s="0">
@@ -507,7 +507,7 @@
       </c>
       <c r="I9" t="inlineStr" s="0">
         <is>
-          <t>Official CS and AI school profiles partially extracted; continue by department</t>
+          <t>Official CS and AI school profiles partially extracted and local thermophysics rows imported; continue by department</t>
         </is>
       </c>
     </row>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="E84" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Energy and power related faculty first pass</t>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="0">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="H84" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I84" t="inlineStr" s="0">
         <is>
-          <t>Strong for energy power systems and electrical engineering</t>
+          <t>Strong for energy power systems and electrical engineering; local workbook rows imported</t>
         </is>
       </c>
     </row>

--- a/workbooks/professor_collection_queue.xlsx
+++ b/workbooks/professor_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:44Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:44Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -957,27 +957,27 @@
       </c>
       <c r="E19" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G19" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://en-cs.hust.edu.cn</t>
         </is>
       </c>
       <c r="H19" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr" s="0">
         <is>
-          <t>Very strong for engineering medicine and applied sciences</t>
+          <t>Official CS faculty profiles partially extracted; continue by institute</t>
         </is>
       </c>
     </row>
@@ -1709,27 +1709,27 @@
       </c>
       <c r="E35" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G35" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://cse.sysu.edu.cn</t>
         </is>
       </c>
       <c r="H35" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I35" t="inlineStr" s="0">
         <is>
-          <t>Top South China option with strong medicine life science and social science</t>
+          <t>Official SYSU faculty profiles partially extracted from School of Computer Science and Engineering</t>
         </is>
       </c>
     </row>
@@ -1756,27 +1756,27 @@
       </c>
       <c r="E36" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G36" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://cic.tju.edu.cn</t>
         </is>
       </c>
       <c r="H36" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I36" t="inlineStr" s="0">
         <is>
-          <t>Excellent engineering and chemical technology target</t>
+          <t>Official faculty profiles partially extracted from School of Computer Science and College of Intelligence and Computing</t>
         </is>
       </c>
     </row>
@@ -1897,27 +1897,27 @@
       </c>
       <c r="E39" t="inlineStr" s="0">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="0">
         <is>
-          <t>All departments and professors</t>
+          <t>Computer science related faculty first pass</t>
         </is>
       </c>
       <c r="G39" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://www.whu.edu.cn</t>
         </is>
       </c>
       <c r="H39" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="I39" t="inlineStr" s="0">
         <is>
-          <t>Strong comprehensive university with strong GIS remote sensing law and sciences</t>
+          <t>Official Wuhan University faculty profiles partially extracted for School of Computer Science</t>
         </is>
       </c>
     </row>

--- a/workbooks/professor_collection_queue.xlsx
+++ b/workbooks/professor_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:44Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:44Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/professor_collection_queue.xlsx
+++ b/workbooks/professor_collection_queue.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Queue</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:57:18Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:57:18Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
